--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,17 +16,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1782676695" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1782676695" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1782676695" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1782676695"/>
+      <pm:revision xmlns:pm="smNativeData" day="1782868662" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1782868662" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1782868662" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1782868662"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2137" uniqueCount="433">
   <si>
     <t>Movie Name</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>English</t>
+  </si>
+  <si>
+    <t>1917</t>
   </si>
   <si>
     <t>Dolby ATMOS</t>
@@ -234,22 +237,22 @@
     <t>Bajirao Mastani</t>
   </si>
   <si>
-    <t>Band of Brothers 1 &amp; 2</t>
+    <t>Band of Brothers (miniseries) 1 &amp; 2</t>
   </si>
   <si>
     <t>Set-18</t>
   </si>
   <si>
-    <t>Band of Brothers 3 &amp; 4</t>
-  </si>
-  <si>
-    <t>Band of Brothers 5 &amp; 6</t>
-  </si>
-  <si>
-    <t>Band of Brothers 7 &amp; 8</t>
-  </si>
-  <si>
-    <t>Band of Brothers 9 &amp; 10</t>
+    <t>Band of Brothers (miniseries) 3 &amp; 4</t>
+  </si>
+  <si>
+    <t>Band of Brothers (miniseries) 5 &amp; 6</t>
+  </si>
+  <si>
+    <t>Band of Brothers (miniseries) 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>Band of Brothers (miniseries) 9 &amp; 10</t>
   </si>
   <si>
     <t>Baraka</t>
@@ -326,10 +329,10 @@
     </r>
   </si>
   <si>
-    <t>Black Panther 1</t>
-  </si>
-  <si>
-    <t>Black Panther 2 - Wakanda Forever</t>
+    <t>Black Panther</t>
+  </si>
+  <si>
+    <t>Wakanda Forever</t>
   </si>
   <si>
     <t>Blade Runner 2049</t>
@@ -413,19 +416,19 @@
     <t>T</t>
   </si>
   <si>
-    <t>Cosmos - A SpaceTime Odyssey - 1</t>
+    <t>Cosmos: A SpaceTime Odyssey - 1</t>
   </si>
   <si>
     <t>Set-34</t>
   </si>
   <si>
-    <t>Cosmos - A SpaceTime Odyssey - 2</t>
-  </si>
-  <si>
-    <t>Cosmos - A SpaceTime Odyssey - 3</t>
-  </si>
-  <si>
-    <t>Cosmos - A SpaceTime Odyssey - 4</t>
+    <t>Cosmos: A SpaceTime Odyssey - 2</t>
+  </si>
+  <si>
+    <t>Cosmos: A SpaceTime Odyssey - 3</t>
+  </si>
+  <si>
+    <t>Cosmos: A SpaceTime Odyssey - 4</t>
   </si>
   <si>
     <t>Creed</t>
@@ -626,22 +629,22 @@
     <t>Flight of the Phoenix</t>
   </si>
   <si>
-    <t>From the Earth To the Moon - 1</t>
+    <t>From the Earth To the Moon (miniseries) - 1</t>
   </si>
   <si>
     <t>Set-35</t>
   </si>
   <si>
-    <t>From the Earth To the Moon - 2</t>
-  </si>
-  <si>
-    <t>From the Earth To the Moon - 3</t>
-  </si>
-  <si>
-    <t>From the Earth To the Moon - 4</t>
-  </si>
-  <si>
-    <t>From the Earth To the Moon - 5</t>
+    <t>From the Earth To the Moon (miniseries) - 2</t>
+  </si>
+  <si>
+    <t>From the Earth To the Moon (miniseries) - 3</t>
+  </si>
+  <si>
+    <t>From the Earth To the Moon (miniseries) - 4</t>
+  </si>
+  <si>
+    <t>From the Earth To the Moon (miniseries) - 5</t>
   </si>
   <si>
     <t>Fury</t>
@@ -674,16 +677,16 @@
     <t>Gladiator</t>
   </si>
   <si>
-    <t>God Father - I</t>
+    <t>God Father (film series) - I</t>
   </si>
   <si>
     <t>Set-12</t>
   </si>
   <si>
-    <t>God Father - II</t>
-  </si>
-  <si>
-    <t>God Father - III</t>
+    <t>God Father (film series) - II</t>
+  </si>
+  <si>
+    <t>God Father (film series) - III</t>
   </si>
   <si>
     <t>Gods of Egypt</t>
@@ -1079,7 +1082,7 @@
     <t>Oppenheimer</t>
   </si>
   <si>
-    <t>Pacific 1 &amp; 2</t>
+    <t>Pacific (miniseries) - 1 &amp; 2</t>
   </si>
   <si>
     <t>Set-27</t>
@@ -1088,16 +1091,16 @@
     <t>P</t>
   </si>
   <si>
-    <t>Pacific 3 &amp; 4</t>
-  </si>
-  <si>
-    <t>Pacific 5 &amp; 6</t>
-  </si>
-  <si>
-    <t>Pacific 7 &amp; 8</t>
-  </si>
-  <si>
-    <t>Pacific 9 &amp; 10</t>
+    <t>Pacific (miniseries) - 3 &amp; 4</t>
+  </si>
+  <si>
+    <t>Pacific (miniseries) - 5 &amp; 6</t>
+  </si>
+  <si>
+    <t>Pacific (miniseries) - 7 &amp; 8</t>
+  </si>
+  <si>
+    <t>Pacific (miniseries) - 9 &amp; 10</t>
   </si>
   <si>
     <t>Pacific Rim</t>
@@ -1178,19 +1181,19 @@
     <t>R</t>
   </si>
   <si>
-    <t>Rambo 1 - First Blood</t>
+    <t>First Blood</t>
   </si>
   <si>
     <t>Set-21</t>
   </si>
   <si>
-    <t>Rambo 2 - First Blood Part II</t>
-  </si>
-  <si>
-    <t>Rambo 3</t>
-  </si>
-  <si>
-    <t>Rambo 4 - The Fight Continues</t>
+    <t>Rambo: First Blood Part II</t>
+  </si>
+  <si>
+    <t>Rambo III</t>
+  </si>
+  <si>
+    <t>Rambo: The Fight Continues</t>
   </si>
   <si>
     <t>Ratatouille</t>
@@ -1247,31 +1250,31 @@
     <t>Set-41</t>
   </si>
   <si>
-    <t>Spider-Man - Far From Home</t>
+    <t>Spider-Man: Far From Home</t>
   </si>
   <si>
     <t>Set-15</t>
   </si>
   <si>
-    <t>Spider-Man - Home Coming</t>
-  </si>
-  <si>
-    <t>Spider-Man - No Way Home</t>
-  </si>
-  <si>
-    <t>Star Trek - Into Darkness</t>
-  </si>
-  <si>
-    <t>Star Wars IV - A New Hope</t>
+    <t>Spider-Man: Home Coming</t>
+  </si>
+  <si>
+    <t>Spider-Man: No Way Home</t>
+  </si>
+  <si>
+    <t>Star Trek Into Darkness</t>
+  </si>
+  <si>
+    <t>Star Wars: Episode IV - A New Hope</t>
   </si>
   <si>
     <t>Dolby Digital 5.1EX</t>
   </si>
   <si>
-    <t>Star Wars V - The Empire Strikes Back</t>
-  </si>
-  <si>
-    <t>Star Wars VI - Return of the Jedi</t>
+    <t>Star Wars: Episode V - The Empire Strikes Back</t>
+  </si>
+  <si>
+    <t>Star Wars: Episode VI - Return of the Jedi</t>
   </si>
   <si>
     <t>Stealth</t>
@@ -1447,7 +1450,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782676695" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1462,7 +1465,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782676695" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1478,7 +1481,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782676695" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1494,7 +1497,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782676695" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1516,7 +1519,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782676695" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1530,7 +1533,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782676695" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1540,22 +1543,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFF9E"/>
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782676695" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF9E"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782676695" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1577,7 +1580,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695"/>
+          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
         </ext>
       </extLst>
     </border>
@@ -1596,7 +1599,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695">
+          <pm:border xmlns:pm="smNativeData" id="1782868662">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1620,7 +1623,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695">
+          <pm:border xmlns:pm="smNativeData" id="1782868662">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1644,7 +1647,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695">
+          <pm:border xmlns:pm="smNativeData" id="1782868662">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1667,7 +1670,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695">
+          <pm:border xmlns:pm="smNativeData" id="1782868662">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1690,7 +1693,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695"/>
+          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
         </ext>
       </extLst>
     </border>
@@ -1709,7 +1712,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782676695"/>
+          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
         </ext>
       </extLst>
     </border>
@@ -1724,7 +1727,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -1732,11 +1735,12 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1782676695" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1782868662" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1782676695" count="1">
+      <pm:colors xmlns:pm="smNativeData" id="1782868662" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
+        <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -2066,8 +2070,8 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="3" t="n">
-        <v>1947</v>
+      <c r="A3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
@@ -2082,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -2093,7 +2097,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
@@ -2102,11 +2106,11 @@
       <c r="D4" s="2"/>
       <c r="E4" s="5"/>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
@@ -2117,7 +2121,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
@@ -2128,7 +2132,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>12</v>
@@ -2139,7 +2143,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
@@ -2154,7 +2158,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
@@ -2165,7 +2169,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
@@ -2174,11 +2178,11 @@
       <c r="D7" s="2"/>
       <c r="E7" s="5"/>
       <c r="F7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -2189,7 +2193,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
@@ -2198,11 +2202,11 @@
       <c r="D8" s="2"/>
       <c r="E8" s="5"/>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
@@ -2213,7 +2217,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
@@ -2228,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" t="s">
         <v>12</v>
@@ -2239,7 +2243,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
@@ -2250,18 +2254,18 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>1</v>
@@ -2272,18 +2276,18 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
         <v>25</v>
-      </c>
-      <c r="I11" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1</v>
@@ -2294,18 +2298,18 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
         <v>25</v>
-      </c>
-      <c r="I12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
@@ -2318,7 +2322,7 @@
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
         <v>12</v>
@@ -2329,7 +2333,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2340,10 +2344,10 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J14" t="s">
         <v>13</v>
@@ -2351,7 +2355,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -2366,10 +2370,10 @@
         <v>6</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J15" t="s">
         <v>13</v>
@@ -2377,7 +2381,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
@@ -2388,10 +2392,10 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J16" t="s">
         <v>13</v>
@@ -2399,7 +2403,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
@@ -2414,10 +2418,10 @@
         <v>6</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" t="s">
         <v>13</v>
@@ -2425,7 +2429,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -2440,10 +2444,10 @@
         <v>6</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" t="s">
         <v>13</v>
@@ -2451,7 +2455,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
@@ -2462,10 +2466,10 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J19" t="s">
         <v>13</v>
@@ -2473,7 +2477,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
@@ -2488,10 +2492,10 @@
         <v>6</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" t="s">
         <v>13</v>
@@ -2499,7 +2503,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2510,10 +2514,10 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J21" t="s">
         <v>13</v>
@@ -2521,7 +2525,7 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
@@ -2532,10 +2536,10 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J22" t="s">
         <v>13</v>
@@ -2543,7 +2547,7 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
@@ -2552,14 +2556,14 @@
       <c r="D23" s="2"/>
       <c r="E23" s="5"/>
       <c r="F23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J23" t="s">
         <v>13</v>
@@ -2567,7 +2571,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>1</v>
@@ -2584,10 +2588,10 @@
         <v>6</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J24" t="s">
         <v>13</v>
@@ -2595,7 +2599,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
@@ -2610,10 +2614,10 @@
         <v>6</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J25" t="s">
         <v>13</v>
@@ -2621,7 +2625,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>1</v>
@@ -2638,10 +2642,10 @@
         <v>6</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" t="s">
         <v>13</v>
@@ -2649,7 +2653,7 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>1</v>
@@ -2660,16 +2664,16 @@
       <c r="D27" s="2"/>
       <c r="E27" s="5"/>
       <c r="F27" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J27" t="s">
         <v>13</v>
@@ -2677,7 +2681,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1</v>
@@ -2688,16 +2692,16 @@
       <c r="D28" s="2"/>
       <c r="E28" s="5"/>
       <c r="F28" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J28" t="s">
         <v>13</v>
@@ -2705,7 +2709,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>1</v>
@@ -2716,16 +2720,16 @@
       <c r="D29" s="2"/>
       <c r="E29" s="5"/>
       <c r="F29" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J29" t="s">
         <v>13</v>
@@ -2733,7 +2737,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2" t="s">
@@ -2744,18 +2748,18 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2" t="s">
@@ -2766,18 +2770,18 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2" t="s">
@@ -2788,18 +2792,18 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
@@ -2808,14 +2812,14 @@
       <c r="D33" s="2"/>
       <c r="E33" s="5"/>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J33" t="s">
         <v>13</v>
@@ -2823,7 +2827,7 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2" t="s">
@@ -2832,14 +2836,14 @@
       <c r="D34" s="2"/>
       <c r="E34" s="5"/>
       <c r="F34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J34" t="s">
         <v>13</v>
@@ -2847,7 +2851,7 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2" t="s">
@@ -2856,14 +2860,14 @@
       <c r="D35" s="2"/>
       <c r="E35" s="5"/>
       <c r="F35" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J35" t="s">
         <v>13</v>
@@ -2871,7 +2875,7 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2" t="s">
@@ -2880,14 +2884,14 @@
       <c r="D36" s="2"/>
       <c r="E36" s="5"/>
       <c r="F36" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J36" t="s">
         <v>13</v>
@@ -2895,7 +2899,7 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
@@ -2904,14 +2908,14 @@
       <c r="D37" s="2"/>
       <c r="E37" s="5"/>
       <c r="F37" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J37" t="s">
         <v>13</v>
@@ -2919,7 +2923,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2" t="s">
@@ -2930,10 +2934,10 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J38" t="s">
         <v>13</v>
@@ -2941,7 +2945,7 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>1</v>
@@ -2952,10 +2956,10 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J39" t="s">
         <v>13</v>
@@ -2963,7 +2967,7 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
@@ -2972,14 +2976,14 @@
       <c r="D40" s="2"/>
       <c r="E40" s="5"/>
       <c r="F40" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J40" t="s">
         <v>13</v>
@@ -2987,7 +2991,7 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2998,10 +3002,10 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J41" t="s">
         <v>13</v>
@@ -3009,7 +3013,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2" t="s">
@@ -3018,14 +3022,14 @@
       <c r="D42" s="2"/>
       <c r="E42" s="5"/>
       <c r="F42" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J42" t="s">
         <v>13</v>
@@ -3033,7 +3037,7 @@
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2" t="s">
@@ -3042,14 +3046,14 @@
       <c r="D43" s="2"/>
       <c r="E43" s="5"/>
       <c r="F43" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J43" t="s">
         <v>13</v>
@@ -3057,7 +3061,7 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
@@ -3072,10 +3076,10 @@
         <v>6</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J44" t="s">
         <v>13</v>
@@ -3083,7 +3087,7 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2" t="s">
@@ -3098,10 +3102,10 @@
         <v>6</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J45" t="s">
         <v>13</v>
@@ -3109,7 +3113,7 @@
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2" t="s">
@@ -3124,10 +3128,10 @@
         <v>6</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J46" t="s">
         <v>13</v>
@@ -3135,7 +3139,7 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3144,14 +3148,14 @@
         <v>4</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J47" t="s">
         <v>13</v>
@@ -3159,7 +3163,7 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3168,14 +3172,14 @@
         <v>4</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J48" t="s">
         <v>13</v>
@@ -3183,7 +3187,7 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3192,14 +3196,14 @@
         <v>4</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J49" t="s">
         <v>13</v>
@@ -3207,7 +3211,7 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3216,14 +3220,14 @@
         <v>4</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J50" t="s">
         <v>13</v>
@@ -3231,7 +3235,7 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>1</v>
@@ -3246,10 +3250,10 @@
         <v>6</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J51" t="s">
         <v>13</v>
@@ -3257,7 +3261,7 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3266,14 +3270,14 @@
         <v>4</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J52" t="s">
         <v>13</v>
@@ -3281,7 +3285,7 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>1</v>
@@ -3296,10 +3300,10 @@
         <v>6</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J53" t="s">
         <v>13</v>
@@ -3307,7 +3311,7 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3316,14 +3320,14 @@
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J54" t="s">
         <v>13</v>
@@ -3331,7 +3335,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3340,14 +3344,14 @@
         <v>4</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J55" t="s">
         <v>13</v>
@@ -3355,7 +3359,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>1</v>
@@ -3370,10 +3374,10 @@
         <v>6</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J56" t="s">
         <v>13</v>
@@ -3381,7 +3385,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3390,14 +3394,14 @@
         <v>4</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J57" t="s">
         <v>13</v>
@@ -3405,7 +3409,7 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>1</v>
@@ -3420,10 +3424,10 @@
         <v>6</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J58" t="s">
         <v>13</v>
@@ -3431,7 +3435,7 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>1</v>
@@ -3440,11 +3444,11 @@
       <c r="D59" s="2"/>
       <c r="E59" s="5"/>
       <c r="F59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I59" t="s">
         <v>1</v>
@@ -3455,7 +3459,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2" t="s">
@@ -3464,14 +3468,14 @@
       <c r="D60" s="2"/>
       <c r="E60" s="5"/>
       <c r="F60" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I60" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s">
         <v>13</v>
@@ -3479,7 +3483,7 @@
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>1</v>
@@ -3494,10 +3498,10 @@
         <v>6</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J61" t="s">
         <v>13</v>
@@ -3505,7 +3509,7 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>1</v>
@@ -3514,11 +3518,11 @@
       <c r="D62" s="2"/>
       <c r="E62" s="5"/>
       <c r="F62" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I62" t="s">
         <v>1</v>
@@ -3529,7 +3533,7 @@
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>1</v>
@@ -3540,18 +3544,18 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
         <v>25</v>
-      </c>
-      <c r="I63" t="s">
-        <v>1</v>
-      </c>
-      <c r="J63" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>1</v>
@@ -3562,7 +3566,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s">
         <v>1</v>
@@ -3573,7 +3577,7 @@
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2" t="s">
@@ -3584,10 +3588,10 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J65" t="s">
         <v>13</v>
@@ -3595,7 +3599,7 @@
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2" t="s">
@@ -3604,14 +3608,14 @@
       <c r="D66" s="2"/>
       <c r="E66" s="5"/>
       <c r="F66" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s">
         <v>13</v>
@@ -3619,7 +3623,7 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
@@ -3628,14 +3632,14 @@
       <c r="D67" s="2"/>
       <c r="E67" s="5"/>
       <c r="F67" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s">
         <v>13</v>
@@ -3643,7 +3647,7 @@
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2" t="s">
@@ -3652,14 +3656,14 @@
       <c r="D68" s="2"/>
       <c r="E68" s="5"/>
       <c r="F68" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J68" t="s">
         <v>13</v>
@@ -3667,7 +3671,7 @@
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2" t="s">
@@ -3676,14 +3680,14 @@
       <c r="D69" s="2"/>
       <c r="E69" s="5"/>
       <c r="F69" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J69" t="s">
         <v>13</v>
@@ -3691,7 +3695,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2" t="s">
@@ -3700,14 +3704,14 @@
       <c r="D70" s="2"/>
       <c r="E70" s="5"/>
       <c r="F70" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J70" t="s">
         <v>13</v>
@@ -3715,7 +3719,7 @@
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2" t="s">
@@ -3730,10 +3734,10 @@
         <v>6</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J71" t="s">
         <v>13</v>
@@ -3741,7 +3745,7 @@
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
@@ -3755,7 +3759,7 @@
         <v>11</v>
       </c>
       <c r="I72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J72" t="s">
         <v>13</v>
@@ -3763,7 +3767,7 @@
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>1</v>
@@ -3774,18 +3778,18 @@
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I73" t="s">
         <v>1</v>
       </c>
       <c r="J73" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>1</v>
@@ -3796,7 +3800,7 @@
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I74" t="s">
         <v>1</v>
@@ -3807,7 +3811,7 @@
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
@@ -3818,10 +3822,10 @@
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I75" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J75" t="s">
         <v>13</v>
@@ -3829,7 +3833,7 @@
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3843,7 +3847,7 @@
         <v>11</v>
       </c>
       <c r="I76" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J76" t="s">
         <v>13</v>
@@ -3851,7 +3855,7 @@
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2" t="s">
@@ -3866,10 +3870,10 @@
         <v>6</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I77" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J77" t="s">
         <v>13</v>
@@ -3877,7 +3881,7 @@
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>1</v>
@@ -3892,10 +3896,10 @@
         <v>6</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J78" t="s">
         <v>13</v>
@@ -3903,7 +3907,7 @@
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
@@ -3918,10 +3922,10 @@
         <v>6</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I79" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J79" t="s">
         <v>13</v>
@@ -3929,7 +3933,7 @@
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>1</v>
@@ -3938,11 +3942,11 @@
       <c r="D80" s="2"/>
       <c r="E80" s="5"/>
       <c r="F80" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I80" t="s">
         <v>1</v>
@@ -3953,7 +3957,7 @@
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>1</v>
@@ -3964,18 +3968,18 @@
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1</v>
+      </c>
+      <c r="J81" t="s">
         <v>25</v>
-      </c>
-      <c r="I81" t="s">
-        <v>1</v>
-      </c>
-      <c r="J81" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>1</v>
@@ -3986,7 +3990,7 @@
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I82" t="s">
         <v>1</v>
@@ -3997,7 +4001,7 @@
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>1</v>
@@ -4008,7 +4012,7 @@
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I83" t="s">
         <v>1</v>
@@ -4019,7 +4023,7 @@
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>1</v>
@@ -4030,7 +4034,7 @@
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I84" t="s">
         <v>1</v>
@@ -4041,7 +4045,7 @@
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>1</v>
@@ -4050,11 +4054,11 @@
       <c r="D85" s="2"/>
       <c r="E85" s="5"/>
       <c r="F85" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I85" t="s">
         <v>1</v>
@@ -4065,7 +4069,7 @@
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>1</v>
@@ -4076,18 +4080,18 @@
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I86" t="s">
         <v>1</v>
       </c>
       <c r="J86" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="2" t="s">
@@ -4098,10 +4102,10 @@
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I87" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J87" t="s">
         <v>13</v>
@@ -4109,7 +4113,7 @@
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>1</v>
@@ -4120,18 +4124,18 @@
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I88" t="s">
+        <v>103</v>
+      </c>
+      <c r="J88" t="s">
         <v>25</v>
-      </c>
-      <c r="I88" t="s">
-        <v>102</v>
-      </c>
-      <c r="J88" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2" t="s">
@@ -4142,10 +4146,10 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J89" t="s">
         <v>13</v>
@@ -4153,7 +4157,7 @@
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4164,10 +4168,10 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I90" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J90" t="s">
         <v>13</v>
@@ -4175,7 +4179,7 @@
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4186,10 +4190,10 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I91" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J91" t="s">
         <v>13</v>
@@ -4197,7 +4201,7 @@
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>1</v>
@@ -4208,18 +4212,18 @@
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I92" t="s">
         <v>1</v>
       </c>
       <c r="J92" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="2" t="s">
@@ -4234,10 +4238,10 @@
         <v>6</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J93" t="s">
         <v>13</v>
@@ -4245,7 +4249,7 @@
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2" t="s">
@@ -4260,10 +4264,10 @@
         <v>6</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J94" t="s">
         <v>13</v>
@@ -4271,7 +4275,7 @@
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="2" t="s">
@@ -4282,10 +4286,10 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I95" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J95" t="s">
         <v>13</v>
@@ -4293,7 +4297,7 @@
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="2" t="s">
@@ -4308,10 +4312,10 @@
         <v>6</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I96" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J96" t="s">
         <v>13</v>
@@ -4319,7 +4323,7 @@
     </row>
     <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4328,14 +4332,14 @@
         <v>4</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J97" t="s">
         <v>13</v>
@@ -4343,7 +4347,7 @@
     </row>
     <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4352,14 +4356,14 @@
         <v>4</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I98" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J98" t="s">
         <v>13</v>
@@ -4367,7 +4371,7 @@
     </row>
     <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4376,14 +4380,14 @@
         <v>4</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G99" s="2"/>
       <c r="H99" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I99" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J99" t="s">
         <v>13</v>
@@ -4391,7 +4395,7 @@
     </row>
     <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>1</v>
@@ -4402,16 +4406,16 @@
       <c r="D100" s="2"/>
       <c r="E100" s="5"/>
       <c r="F100" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I100" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J100" t="s">
         <v>13</v>
@@ -4419,7 +4423,7 @@
     </row>
     <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2" t="s">
@@ -4428,14 +4432,14 @@
       <c r="D101" s="2"/>
       <c r="E101" s="5"/>
       <c r="F101" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G101" s="2"/>
       <c r="H101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J101" t="s">
         <v>13</v>
@@ -4443,7 +4447,7 @@
     </row>
     <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>1</v>
@@ -4458,10 +4462,10 @@
         <v>6</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I102" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J102" t="s">
         <v>13</v>
@@ -4469,7 +4473,7 @@
     </row>
     <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="2" t="s">
@@ -4480,10 +4484,10 @@
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I103" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J103" t="s">
         <v>13</v>
@@ -4491,7 +4495,7 @@
     </row>
     <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>1</v>
@@ -4506,10 +4510,10 @@
         <v>6</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I104" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J104" t="s">
         <v>13</v>
@@ -4517,7 +4521,7 @@
     </row>
     <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="2" t="s">
@@ -4528,10 +4532,10 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I105" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J105" t="s">
         <v>13</v>
@@ -4539,7 +4543,7 @@
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>1</v>
@@ -4554,10 +4558,10 @@
         <v>6</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I106" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J106" t="s">
         <v>13</v>
@@ -4565,7 +4569,7 @@
     </row>
     <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4576,10 +4580,10 @@
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I107" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J107" t="s">
         <v>13</v>
@@ -4587,7 +4591,7 @@
     </row>
     <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4598,10 +4602,10 @@
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I108" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J108" t="s">
         <v>13</v>
@@ -4609,7 +4613,7 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>1</v>
@@ -4620,18 +4624,18 @@
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I109" t="s">
+        <v>1</v>
+      </c>
+      <c r="J109" t="s">
         <v>25</v>
-      </c>
-      <c r="I109" t="s">
-        <v>1</v>
-      </c>
-      <c r="J109" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>1</v>
@@ -4642,18 +4646,18 @@
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I110" t="s">
         <v>1</v>
       </c>
       <c r="J110" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2" t="s">
@@ -4668,10 +4672,10 @@
         <v>6</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J111" t="s">
         <v>13</v>
@@ -4679,7 +4683,7 @@
     </row>
     <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2" t="s">
@@ -4688,14 +4692,14 @@
       <c r="D112" s="2"/>
       <c r="E112" s="5"/>
       <c r="F112" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G112" s="2"/>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J112" t="s">
         <v>13</v>
@@ -4703,7 +4707,7 @@
     </row>
     <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" s="2" t="s">
@@ -4718,10 +4722,10 @@
         <v>6</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J113" t="s">
         <v>13</v>
@@ -4729,7 +4733,7 @@
     </row>
     <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" s="2" t="s">
@@ -4738,14 +4742,14 @@
       <c r="D114" s="2"/>
       <c r="E114" s="5"/>
       <c r="F114" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G114" s="2"/>
       <c r="H114" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J114" t="s">
         <v>13</v>
@@ -4753,7 +4757,7 @@
     </row>
     <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" s="2" t="s">
@@ -4762,14 +4766,14 @@
       <c r="D115" s="2"/>
       <c r="E115" s="5"/>
       <c r="F115" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G115" s="2"/>
       <c r="H115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J115" t="s">
         <v>13</v>
@@ -4777,7 +4781,7 @@
     </row>
     <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2" t="s">
@@ -4786,14 +4790,14 @@
       <c r="D116" s="2"/>
       <c r="E116" s="5"/>
       <c r="F116" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G116" s="2"/>
       <c r="H116" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J116" t="s">
         <v>13</v>
@@ -4801,7 +4805,7 @@
     </row>
     <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B117" s="2"/>
       <c r="C117" s="2" t="s">
@@ -4810,14 +4814,14 @@
       <c r="D117" s="2"/>
       <c r="E117" s="5"/>
       <c r="F117" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G117" s="2"/>
       <c r="H117" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J117" t="s">
         <v>13</v>
@@ -4825,7 +4829,7 @@
     </row>
     <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" s="2" t="s">
@@ -4834,14 +4838,14 @@
       <c r="D118" s="2"/>
       <c r="E118" s="5"/>
       <c r="F118" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G118" s="2"/>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J118" t="s">
         <v>13</v>
@@ -4849,7 +4853,7 @@
     </row>
     <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" s="2" t="s">
@@ -4864,10 +4868,10 @@
         <v>6</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I119" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J119" t="s">
         <v>13</v>
@@ -4875,7 +4879,7 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="s">
@@ -4890,10 +4894,10 @@
         <v>6</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J120" t="s">
         <v>13</v>
@@ -4901,7 +4905,7 @@
     </row>
     <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" s="2" t="s">
@@ -4916,10 +4920,10 @@
         <v>6</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J121" t="s">
         <v>13</v>
@@ -4927,7 +4931,7 @@
     </row>
     <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" s="2" t="s">
@@ -4938,10 +4942,10 @@
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I122" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J122" t="s">
         <v>13</v>
@@ -4949,7 +4953,7 @@
     </row>
     <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" s="2" t="s">
@@ -4966,10 +4970,10 @@
         <v>6</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I123" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J123" t="s">
         <v>13</v>
@@ -4977,7 +4981,7 @@
     </row>
     <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B124" s="2"/>
       <c r="C124" s="2" t="s">
@@ -4988,10 +4992,10 @@
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J124" t="s">
         <v>13</v>
@@ -4999,7 +5003,7 @@
     </row>
     <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>1</v>
@@ -5008,11 +5012,11 @@
       <c r="D125" s="2"/>
       <c r="E125" s="5"/>
       <c r="F125" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G125" s="2"/>
       <c r="H125" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I125" t="s">
         <v>1</v>
@@ -5023,7 +5027,7 @@
     </row>
     <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>1</v>
@@ -5032,11 +5036,11 @@
       <c r="D126" s="2"/>
       <c r="E126" s="5"/>
       <c r="F126" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G126" s="2"/>
       <c r="H126" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I126" t="s">
         <v>1</v>
@@ -5047,7 +5051,7 @@
     </row>
     <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>1</v>
@@ -5056,11 +5060,11 @@
       <c r="D127" s="2"/>
       <c r="E127" s="5"/>
       <c r="F127" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G127" s="2"/>
       <c r="H127" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I127" t="s">
         <v>1</v>
@@ -5071,7 +5075,7 @@
     </row>
     <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>1</v>
@@ -5080,11 +5084,11 @@
       <c r="D128" s="2"/>
       <c r="E128" s="5"/>
       <c r="F128" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G128" s="2"/>
       <c r="H128" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I128" t="s">
         <v>1</v>
@@ -5095,7 +5099,7 @@
     </row>
     <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>1</v>
@@ -5104,11 +5108,11 @@
       <c r="D129" s="2"/>
       <c r="E129" s="5"/>
       <c r="F129" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G129" s="2"/>
       <c r="H129" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I129" t="s">
         <v>1</v>
@@ -5119,7 +5123,7 @@
     </row>
     <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="2" t="s">
@@ -5130,10 +5134,10 @@
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J130" t="s">
         <v>13</v>
@@ -5141,7 +5145,7 @@
     </row>
     <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>1</v>
@@ -5152,7 +5156,7 @@
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I131" t="s">
         <v>1</v>
@@ -5163,7 +5167,7 @@
     </row>
     <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="2" t="s">
@@ -5177,7 +5181,7 @@
         <v>11</v>
       </c>
       <c r="I132" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J132" t="s">
         <v>13</v>
@@ -5185,7 +5189,7 @@
     </row>
     <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="2" t="s">
@@ -5200,10 +5204,10 @@
         <v>6</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I133" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J133" t="s">
         <v>13</v>
@@ -5211,7 +5215,7 @@
     </row>
     <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>1</v>
@@ -5222,18 +5226,18 @@
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I134" t="s">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
         <v>25</v>
-      </c>
-      <c r="I134" t="s">
-        <v>1</v>
-      </c>
-      <c r="J134" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -5247,7 +5251,7 @@
         <v>11</v>
       </c>
       <c r="I135" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J135" t="s">
         <v>13</v>
@@ -5255,7 +5259,7 @@
     </row>
     <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5266,10 +5270,10 @@
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I136" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J136" t="s">
         <v>13</v>
@@ -5277,7 +5281,7 @@
     </row>
     <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5288,10 +5292,10 @@
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I137" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J137" t="s">
         <v>13</v>
@@ -5299,7 +5303,7 @@
     </row>
     <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" s="2" t="s">
@@ -5314,10 +5318,10 @@
         <v>6</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I138" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J138" t="s">
         <v>13</v>
@@ -5325,7 +5329,7 @@
     </row>
     <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" s="2" t="s">
@@ -5334,14 +5338,14 @@
       <c r="D139" s="2"/>
       <c r="E139" s="5"/>
       <c r="F139" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G139" s="2"/>
       <c r="H139" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I139" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J139" t="s">
         <v>13</v>
@@ -5349,7 +5353,7 @@
     </row>
     <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="2" t="s">
@@ -5358,14 +5362,14 @@
       <c r="D140" s="2"/>
       <c r="E140" s="5"/>
       <c r="F140" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G140" s="2"/>
       <c r="H140" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I140" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J140" t="s">
         <v>13</v>
@@ -5373,7 +5377,7 @@
     </row>
     <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="2" t="s">
@@ -5382,14 +5386,14 @@
       <c r="D141" s="2"/>
       <c r="E141" s="5"/>
       <c r="F141" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G141" s="2"/>
       <c r="H141" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I141" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J141" t="s">
         <v>13</v>
@@ -5397,7 +5401,7 @@
     </row>
     <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="2" t="s">
@@ -5408,10 +5412,10 @@
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I142" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J142" t="s">
         <v>13</v>
@@ -5419,7 +5423,7 @@
     </row>
     <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5430,10 +5434,10 @@
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I143" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J143" t="s">
         <v>13</v>
@@ -5441,7 +5445,7 @@
     </row>
     <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5450,14 +5454,14 @@
         <v>4</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G144" s="2"/>
       <c r="H144" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I144" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J144" t="s">
         <v>13</v>
@@ -5465,7 +5469,7 @@
     </row>
     <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5474,14 +5478,14 @@
         <v>4</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G145" s="2"/>
       <c r="H145" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I145" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J145" t="s">
         <v>13</v>
@@ -5489,7 +5493,7 @@
     </row>
     <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5498,14 +5502,14 @@
         <v>4</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G146" s="2"/>
       <c r="H146" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I146" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J146" t="s">
         <v>13</v>
@@ -5513,7 +5517,7 @@
     </row>
     <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5527,7 +5531,7 @@
         <v>11</v>
       </c>
       <c r="I147" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J147" t="s">
         <v>13</v>
@@ -5535,7 +5539,7 @@
     </row>
     <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5544,14 +5548,14 @@
         <v>4</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G148" s="2"/>
       <c r="H148" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I148" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J148" t="s">
         <v>13</v>
@@ -5559,7 +5563,7 @@
     </row>
     <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B149" s="2"/>
       <c r="C149" s="2" t="s">
@@ -5570,10 +5574,10 @@
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I149" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J149" t="s">
         <v>13</v>
@@ -5581,7 +5585,7 @@
     </row>
     <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>1</v>
@@ -5598,10 +5602,10 @@
         <v>6</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I150" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J150" t="s">
         <v>13</v>
@@ -5609,7 +5613,7 @@
     </row>
     <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" s="2" t="s">
@@ -5624,10 +5628,10 @@
         <v>6</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I151" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J151" t="s">
         <v>13</v>
@@ -5635,7 +5639,7 @@
     </row>
     <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" s="2" t="s">
@@ -5646,10 +5650,10 @@
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I152" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J152" t="s">
         <v>13</v>
@@ -5657,7 +5661,7 @@
     </row>
     <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" s="2" t="s">
@@ -5672,10 +5676,10 @@
         <v>6</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I153" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J153" t="s">
         <v>13</v>
@@ -5683,7 +5687,7 @@
     </row>
     <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>1</v>
@@ -5694,18 +5698,18 @@
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I154" t="s">
+        <v>1</v>
+      </c>
+      <c r="J154" t="s">
         <v>25</v>
-      </c>
-      <c r="I154" t="s">
-        <v>1</v>
-      </c>
-      <c r="J154" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>1</v>
@@ -5716,10 +5720,10 @@
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I155" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J155" t="s">
         <v>13</v>
@@ -5727,7 +5731,7 @@
     </row>
     <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>1</v>
@@ -5744,10 +5748,10 @@
         <v>6</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I156" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J156" t="s">
         <v>13</v>
@@ -5755,7 +5759,7 @@
     </row>
     <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>1</v>
@@ -5772,10 +5776,10 @@
         <v>6</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I157" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J157" t="s">
         <v>13</v>
@@ -5783,7 +5787,7 @@
     </row>
     <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>1</v>
@@ -5794,18 +5798,18 @@
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1</v>
+      </c>
+      <c r="J158" t="s">
         <v>25</v>
-      </c>
-      <c r="I158" t="s">
-        <v>1</v>
-      </c>
-      <c r="J158" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" s="2" t="s">
@@ -5816,10 +5820,10 @@
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I159" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J159" t="s">
         <v>13</v>
@@ -5827,7 +5831,7 @@
     </row>
     <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>1</v>
@@ -5836,11 +5840,11 @@
       <c r="D160" s="2"/>
       <c r="E160" s="5"/>
       <c r="F160" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G160" s="2"/>
       <c r="H160" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I160" t="s">
         <v>1</v>
@@ -5851,7 +5855,7 @@
     </row>
     <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>1</v>
@@ -5860,11 +5864,11 @@
       <c r="D161" s="2"/>
       <c r="E161" s="5"/>
       <c r="F161" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G161" s="2"/>
       <c r="H161" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I161" t="s">
         <v>1</v>
@@ -5875,7 +5879,7 @@
     </row>
     <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>1</v>
@@ -5884,11 +5888,11 @@
       <c r="D162" s="2"/>
       <c r="E162" s="5"/>
       <c r="F162" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G162" s="2"/>
       <c r="H162" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I162" t="s">
         <v>1</v>
@@ -5899,7 +5903,7 @@
     </row>
     <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>1</v>
@@ -5916,10 +5920,10 @@
         <v>6</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I163" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J163" t="s">
         <v>13</v>
@@ -5927,7 +5931,7 @@
     </row>
     <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>1</v>
@@ -5942,10 +5946,10 @@
         <v>6</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I164" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J164" t="s">
         <v>13</v>
@@ -5953,7 +5957,7 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B165" s="2"/>
       <c r="C165" s="2" t="s">
@@ -5968,10 +5972,10 @@
         <v>6</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I165" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J165" t="s">
         <v>13</v>
@@ -5979,7 +5983,7 @@
     </row>
     <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B166" s="2"/>
       <c r="C166" s="2" t="s">
@@ -5988,14 +5992,14 @@
       <c r="D166" s="2"/>
       <c r="E166" s="5"/>
       <c r="F166" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G166" s="2"/>
       <c r="H166" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I166" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J166" t="s">
         <v>13</v>
@@ -6003,7 +6007,7 @@
     </row>
     <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B167" s="2"/>
       <c r="C167" s="2" t="s">
@@ -6018,10 +6022,10 @@
         <v>6</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I167" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J167" t="s">
         <v>13</v>
@@ -6029,7 +6033,7 @@
     </row>
     <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B168" s="2"/>
       <c r="C168" s="2" t="s">
@@ -6044,10 +6048,10 @@
         <v>6</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I168" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J168" t="s">
         <v>13</v>
@@ -6055,7 +6059,7 @@
     </row>
     <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B169" s="2"/>
       <c r="C169" s="2" t="s">
@@ -6070,10 +6074,10 @@
         <v>6</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I169" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J169" t="s">
         <v>13</v>
@@ -6081,7 +6085,7 @@
     </row>
     <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B170" s="2"/>
       <c r="C170" s="2" t="s">
@@ -6092,10 +6096,10 @@
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I170" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J170" t="s">
         <v>13</v>
@@ -6103,7 +6107,7 @@
     </row>
     <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B171" s="2"/>
       <c r="C171" s="2" t="s">
@@ -6112,14 +6116,14 @@
       <c r="D171" s="2"/>
       <c r="E171" s="5"/>
       <c r="F171" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I171" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J171" t="s">
         <v>13</v>
@@ -6127,7 +6131,7 @@
     </row>
     <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" s="2" t="s">
@@ -6136,14 +6140,14 @@
       <c r="D172" s="2"/>
       <c r="E172" s="5"/>
       <c r="F172" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G172" s="2"/>
       <c r="H172" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I172" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J172" t="s">
         <v>13</v>
@@ -6151,7 +6155,7 @@
     </row>
     <row r="173" spans="1:10">
       <c r="A173" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" s="2" t="s">
@@ -6160,14 +6164,14 @@
       <c r="D173" s="2"/>
       <c r="E173" s="5"/>
       <c r="F173" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G173" s="2"/>
       <c r="H173" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I173" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J173" t="s">
         <v>13</v>
@@ -6175,7 +6179,7 @@
     </row>
     <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" s="2" t="s">
@@ -6184,14 +6188,14 @@
       <c r="D174" s="2"/>
       <c r="E174" s="5"/>
       <c r="F174" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G174" s="2"/>
       <c r="H174" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I174" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J174" t="s">
         <v>13</v>
@@ -6199,7 +6203,7 @@
     </row>
     <row r="175" spans="1:10">
       <c r="A175" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B175" s="2"/>
       <c r="C175" s="2" t="s">
@@ -6208,14 +6212,14 @@
       <c r="D175" s="2"/>
       <c r="E175" s="5"/>
       <c r="F175" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G175" s="2"/>
       <c r="H175" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I175" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J175" t="s">
         <v>13</v>
@@ -6223,7 +6227,7 @@
     </row>
     <row r="176" spans="1:10">
       <c r="A176" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6232,14 +6236,14 @@
         <v>4</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G176" s="2"/>
       <c r="H176" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I176" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J176" t="s">
         <v>13</v>
@@ -6247,7 +6251,7 @@
     </row>
     <row r="177" spans="1:10">
       <c r="A177" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>1</v>
@@ -6258,7 +6262,7 @@
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I177" t="s">
         <v>1</v>
@@ -6269,7 +6273,7 @@
     </row>
     <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>1</v>
@@ -6280,18 +6284,18 @@
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I178" t="s">
         <v>1</v>
       </c>
       <c r="J178" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>1</v>
@@ -6308,10 +6312,10 @@
         <v>6</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I179" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J179" t="s">
         <v>13</v>
@@ -6319,7 +6323,7 @@
     </row>
     <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>1</v>
@@ -6334,10 +6338,10 @@
         <v>6</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I180" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J180" t="s">
         <v>13</v>
@@ -6345,7 +6349,7 @@
     </row>
     <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="2" t="s">
@@ -6360,10 +6364,10 @@
         <v>6</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I181" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J181" t="s">
         <v>13</v>
@@ -6371,7 +6375,7 @@
     </row>
     <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="2" t="s">
@@ -6386,10 +6390,10 @@
         <v>6</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I182" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J182" t="s">
         <v>13</v>
@@ -6397,7 +6401,7 @@
     </row>
     <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="2" t="s">
@@ -6412,10 +6416,10 @@
         <v>6</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I183" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J183" t="s">
         <v>13</v>
@@ -6423,7 +6427,7 @@
     </row>
     <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>1</v>
@@ -6440,10 +6444,10 @@
         <v>6</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I184" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J184" t="s">
         <v>13</v>
@@ -6451,7 +6455,7 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6462,10 +6466,10 @@
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I185" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J185" t="s">
         <v>13</v>
@@ -6473,7 +6477,7 @@
     </row>
     <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>1</v>
@@ -6488,10 +6492,10 @@
         <v>6</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I186" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J186" t="s">
         <v>13</v>
@@ -6499,7 +6503,7 @@
     </row>
     <row r="187" spans="1:10">
       <c r="A187" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>1</v>
@@ -6514,10 +6518,10 @@
         <v>6</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I187" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J187" t="s">
         <v>13</v>
@@ -6525,7 +6529,7 @@
     </row>
     <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>1</v>
@@ -6540,10 +6544,10 @@
         <v>6</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I188" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J188" t="s">
         <v>13</v>
@@ -6551,7 +6555,7 @@
     </row>
     <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" s="2" t="s">
@@ -6566,10 +6570,10 @@
         <v>6</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I189" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J189" t="s">
         <v>13</v>
@@ -6577,7 +6581,7 @@
     </row>
     <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>1</v>
@@ -6588,18 +6592,18 @@
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I190" t="s">
+        <v>1</v>
+      </c>
+      <c r="J190" t="s">
         <v>25</v>
-      </c>
-      <c r="I190" t="s">
-        <v>1</v>
-      </c>
-      <c r="J190" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>1</v>
@@ -6610,18 +6614,18 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I191" t="s">
         <v>1</v>
       </c>
       <c r="J191" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="2" t="s">
@@ -6632,10 +6636,10 @@
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I192" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J192" t="s">
         <v>13</v>
@@ -6643,7 +6647,7 @@
     </row>
     <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="2" t="s">
@@ -6654,10 +6658,10 @@
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I193" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J193" t="s">
         <v>13</v>
@@ -6665,7 +6669,7 @@
     </row>
     <row r="194" spans="1:10">
       <c r="A194" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="2" t="s">
@@ -6674,14 +6678,14 @@
       <c r="D194" s="2"/>
       <c r="E194" s="5"/>
       <c r="F194" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G194" s="2"/>
       <c r="H194" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I194" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J194" t="s">
         <v>13</v>
@@ -6689,7 +6693,7 @@
     </row>
     <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="2" t="s">
@@ -6698,14 +6702,14 @@
       <c r="D195" s="2"/>
       <c r="E195" s="5"/>
       <c r="F195" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G195" s="2"/>
       <c r="H195" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I195" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J195" t="s">
         <v>13</v>
@@ -6713,7 +6717,7 @@
     </row>
     <row r="196" spans="1:10">
       <c r="A196" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -6722,14 +6726,14 @@
         <v>4</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G196" s="2"/>
       <c r="H196" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I196" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J196" t="s">
         <v>13</v>
@@ -6737,7 +6741,7 @@
     </row>
     <row r="197" spans="1:10">
       <c r="A197" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>1</v>
@@ -6748,18 +6752,18 @@
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I197" t="s">
+        <v>1</v>
+      </c>
+      <c r="J197" t="s">
         <v>25</v>
-      </c>
-      <c r="I197" t="s">
-        <v>1</v>
-      </c>
-      <c r="J197" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>1</v>
@@ -6770,18 +6774,18 @@
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I198" t="s">
         <v>1</v>
       </c>
       <c r="J198" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2" t="s">
@@ -6790,14 +6794,14 @@
       <c r="D199" s="2"/>
       <c r="E199" s="5"/>
       <c r="F199" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G199" s="2"/>
       <c r="H199" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I199" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J199" t="s">
         <v>13</v>
@@ -6805,7 +6809,7 @@
     </row>
     <row r="200" spans="1:10">
       <c r="A200" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2" t="s">
@@ -6814,14 +6818,14 @@
       <c r="D200" s="2"/>
       <c r="E200" s="5"/>
       <c r="F200" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G200" s="2"/>
       <c r="H200" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I200" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J200" t="s">
         <v>13</v>
@@ -6829,7 +6833,7 @@
     </row>
     <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" s="2" t="s">
@@ -6840,10 +6844,10 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I201" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J201" t="s">
         <v>13</v>
@@ -6851,7 +6855,7 @@
     </row>
     <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" s="2" t="s">
@@ -6860,14 +6864,14 @@
       <c r="D202" s="2"/>
       <c r="E202" s="5"/>
       <c r="F202" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G202" s="2"/>
       <c r="H202" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I202" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J202" t="s">
         <v>13</v>
@@ -6875,7 +6879,7 @@
     </row>
     <row r="203" spans="1:10">
       <c r="A203" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" s="2" t="s">
@@ -6884,14 +6888,14 @@
       <c r="D203" s="2"/>
       <c r="E203" s="5"/>
       <c r="F203" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G203" s="2"/>
       <c r="H203" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I203" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J203" t="s">
         <v>13</v>
@@ -6899,7 +6903,7 @@
     </row>
     <row r="204" spans="1:10">
       <c r="A204" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" s="2" t="s">
@@ -6908,14 +6912,14 @@
       <c r="D204" s="2"/>
       <c r="E204" s="5"/>
       <c r="F204" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I204" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J204" t="s">
         <v>13</v>
@@ -6923,7 +6927,7 @@
     </row>
     <row r="205" spans="1:10">
       <c r="A205" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="2" t="s">
@@ -6932,14 +6936,14 @@
       <c r="D205" s="2"/>
       <c r="E205" s="5"/>
       <c r="F205" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I205" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J205" t="s">
         <v>13</v>
@@ -6947,7 +6951,7 @@
     </row>
     <row r="206" spans="1:10">
       <c r="A206" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>1</v>
@@ -6964,10 +6968,10 @@
         <v>6</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I206" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J206" t="s">
         <v>13</v>
@@ -6975,7 +6979,7 @@
     </row>
     <row r="207" spans="1:10">
       <c r="A207" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B207" s="2"/>
       <c r="C207" s="2" t="s">
@@ -6984,14 +6988,14 @@
       <c r="D207" s="2"/>
       <c r="E207" s="5"/>
       <c r="F207" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I207" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J207" t="s">
         <v>13</v>
@@ -6999,7 +7003,7 @@
     </row>
     <row r="208" spans="1:10">
       <c r="A208" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>1</v>
@@ -7010,18 +7014,18 @@
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I208" t="s">
         <v>1</v>
       </c>
       <c r="J208" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>1</v>
@@ -7036,10 +7040,10 @@
         <v>6</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I209" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J209" t="s">
         <v>13</v>
@@ -7047,7 +7051,7 @@
     </row>
     <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B210" s="2"/>
       <c r="C210" s="2" t="s">
@@ -7062,10 +7066,10 @@
         <v>6</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I210" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J210" t="s">
         <v>13</v>
@@ -7073,7 +7077,7 @@
     </row>
     <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" s="2" t="s">
@@ -7088,10 +7092,10 @@
         <v>6</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I211" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J211" t="s">
         <v>13</v>
@@ -7099,7 +7103,7 @@
     </row>
     <row r="212" spans="1:10">
       <c r="A212" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -7110,10 +7114,10 @@
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I212" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J212" t="s">
         <v>13</v>
@@ -7121,7 +7125,7 @@
     </row>
     <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>1</v>
@@ -7138,10 +7142,10 @@
         <v>6</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I213" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J213" t="s">
         <v>13</v>
@@ -7149,7 +7153,7 @@
     </row>
     <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" s="2" t="s">
@@ -7160,10 +7164,10 @@
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I214" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J214" t="s">
         <v>13</v>
@@ -7171,7 +7175,7 @@
     </row>
     <row r="215" spans="1:10">
       <c r="A215" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>1</v>
@@ -7182,7 +7186,7 @@
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I215" t="s">
         <v>1</v>
@@ -7193,7 +7197,7 @@
     </row>
     <row r="216" spans="1:10">
       <c r="A216" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>1</v>
@@ -7204,7 +7208,7 @@
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I216" t="s">
         <v>1</v>
@@ -7215,7 +7219,7 @@
     </row>
     <row r="217" spans="1:10">
       <c r="A217" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="2" t="s">
@@ -7230,10 +7234,10 @@
         <v>6</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I217" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J217" t="s">
         <v>13</v>
@@ -7241,7 +7245,7 @@
     </row>
     <row r="218" spans="1:10">
       <c r="A218" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B218" s="2"/>
       <c r="C218" s="2" t="s">
@@ -7252,18 +7256,18 @@
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I218" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J218" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B219" s="2"/>
       <c r="C219" s="2" t="s">
@@ -7274,10 +7278,10 @@
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I219" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J219" t="s">
         <v>13</v>
@@ -7285,7 +7289,7 @@
     </row>
     <row r="220" spans="1:10">
       <c r="A220" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" s="2" t="s">
@@ -7296,16 +7300,16 @@
         <v>4</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I220" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J220" t="s">
         <v>13</v>
@@ -7313,7 +7317,7 @@
     </row>
     <row r="221" spans="1:10">
       <c r="A221" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B221" s="2"/>
       <c r="C221" s="2" t="s">
@@ -7324,16 +7328,16 @@
         <v>4</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I221" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J221" t="s">
         <v>13</v>
@@ -7341,7 +7345,7 @@
     </row>
     <row r="222" spans="1:10">
       <c r="A222" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B222" s="2"/>
       <c r="C222" s="2" t="s">
@@ -7352,16 +7356,16 @@
         <v>4</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I222" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J222" t="s">
         <v>13</v>
@@ -7369,7 +7373,7 @@
     </row>
     <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" s="2" t="s">
@@ -7380,16 +7384,16 @@
         <v>4</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I223" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J223" t="s">
         <v>13</v>
@@ -7397,7 +7401,7 @@
     </row>
     <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>1</v>
@@ -7408,7 +7412,7 @@
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I224" t="s">
         <v>1</v>
@@ -7419,7 +7423,7 @@
     </row>
     <row r="225" spans="1:10">
       <c r="A225" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>1</v>
@@ -7428,11 +7432,11 @@
       <c r="D225" s="2"/>
       <c r="E225" s="5"/>
       <c r="F225" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G225" s="2"/>
       <c r="H225" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I225" t="s">
         <v>1</v>
@@ -7443,7 +7447,7 @@
     </row>
     <row r="226" spans="1:10">
       <c r="A226" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>1</v>
@@ -7454,18 +7458,18 @@
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1</v>
+      </c>
+      <c r="J226" t="s">
         <v>25</v>
-      </c>
-      <c r="I226" t="s">
-        <v>1</v>
-      </c>
-      <c r="J226" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="A227" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="2" t="s">
@@ -7480,10 +7484,10 @@
         <v>6</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I227" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J227" t="s">
         <v>13</v>
@@ -7491,7 +7495,7 @@
     </row>
     <row r="228" spans="1:10">
       <c r="A228" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="2" t="s">
@@ -7502,10 +7506,10 @@
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I228" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J228" t="s">
         <v>13</v>
@@ -7513,7 +7517,7 @@
     </row>
     <row r="229" spans="1:10">
       <c r="A229" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="2" t="s">
@@ -7522,14 +7526,14 @@
       <c r="D229" s="2"/>
       <c r="E229" s="5"/>
       <c r="F229" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G229" s="2"/>
       <c r="H229" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I229" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J229" t="s">
         <v>13</v>
@@ -7537,7 +7541,7 @@
     </row>
     <row r="230" spans="1:10">
       <c r="A230" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="2" t="s">
@@ -7546,14 +7550,14 @@
       <c r="D230" s="2"/>
       <c r="E230" s="5"/>
       <c r="F230" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G230" s="2"/>
       <c r="H230" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I230" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J230" t="s">
         <v>13</v>
@@ -7561,7 +7565,7 @@
     </row>
     <row r="231" spans="1:10">
       <c r="A231" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B231" s="2"/>
       <c r="C231" s="2" t="s">
@@ -7570,14 +7574,14 @@
       <c r="D231" s="2"/>
       <c r="E231" s="5"/>
       <c r="F231" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G231" s="2"/>
       <c r="H231" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I231" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J231" t="s">
         <v>13</v>
@@ -7585,7 +7589,7 @@
     </row>
     <row r="232" spans="1:10">
       <c r="A232" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" s="2" t="s">
@@ -7596,10 +7600,10 @@
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I232" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J232" t="s">
         <v>13</v>
@@ -7607,7 +7611,7 @@
     </row>
     <row r="233" spans="1:10">
       <c r="A233" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B233" s="2"/>
       <c r="C233" s="2" t="s">
@@ -7616,14 +7620,14 @@
       <c r="D233" s="2"/>
       <c r="E233" s="5"/>
       <c r="F233" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G233" s="2"/>
       <c r="H233" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I233" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J233" t="s">
         <v>13</v>
@@ -7631,7 +7635,7 @@
     </row>
     <row r="234" spans="1:10">
       <c r="A234" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>1</v>
@@ -7646,10 +7650,10 @@
         <v>6</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I234" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J234" t="s">
         <v>13</v>
@@ -7657,7 +7661,7 @@
     </row>
     <row r="235" spans="1:10">
       <c r="A235" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B235" s="2"/>
       <c r="C235" s="2" t="s">
@@ -7672,10 +7676,10 @@
         <v>6</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I235" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J235" t="s">
         <v>13</v>
@@ -7683,7 +7687,7 @@
     </row>
     <row r="236" spans="1:10">
       <c r="A236" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -7694,10 +7698,10 @@
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I236" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J236" t="s">
         <v>13</v>
@@ -7705,7 +7709,7 @@
     </row>
     <row r="237" spans="1:10">
       <c r="A237" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" s="2" t="s">
@@ -7720,10 +7724,10 @@
         <v>6</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I237" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J237" t="s">
         <v>13</v>
@@ -7731,7 +7735,7 @@
     </row>
     <row r="238" spans="1:10">
       <c r="A238" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B238" s="2"/>
       <c r="C238" s="2" t="s">
@@ -7742,18 +7746,18 @@
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I238" t="s">
+        <v>1</v>
+      </c>
+      <c r="J238" t="s">
         <v>25</v>
-      </c>
-      <c r="I238" t="s">
-        <v>1</v>
-      </c>
-      <c r="J238" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="239" spans="1:10">
       <c r="A239" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="2" t="s">
@@ -7768,10 +7772,10 @@
         <v>6</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I239" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J239" t="s">
         <v>13</v>
@@ -7779,7 +7783,7 @@
     </row>
     <row r="240" spans="1:10">
       <c r="A240" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>1</v>
@@ -7790,7 +7794,7 @@
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I240" t="s">
         <v>1</v>
@@ -7801,7 +7805,7 @@
     </row>
     <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B241" s="2"/>
       <c r="C241" s="2" t="s">
@@ -7812,10 +7816,10 @@
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I241" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J241" t="s">
         <v>13</v>
@@ -7823,7 +7827,7 @@
     </row>
     <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>1</v>
@@ -7834,18 +7838,18 @@
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I242" t="s">
         <v>1</v>
       </c>
       <c r="J242" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>1</v>
@@ -7856,18 +7860,18 @@
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I243" t="s">
         <v>1</v>
       </c>
       <c r="J243" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>1</v>
@@ -7878,18 +7882,18 @@
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I244" t="s">
+        <v>1</v>
+      </c>
+      <c r="J244" t="s">
         <v>25</v>
-      </c>
-      <c r="I244" t="s">
-        <v>1</v>
-      </c>
-      <c r="J244" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>1</v>
@@ -7900,18 +7904,18 @@
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I245" t="s">
+        <v>1</v>
+      </c>
+      <c r="J245" t="s">
         <v>25</v>
-      </c>
-      <c r="I245" t="s">
-        <v>1</v>
-      </c>
-      <c r="J245" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B246" s="2"/>
       <c r="C246" s="2" t="s">
@@ -7922,10 +7926,10 @@
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I246" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J246" t="s">
         <v>13</v>
@@ -7933,7 +7937,7 @@
     </row>
     <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>1</v>
@@ -7948,10 +7952,10 @@
         <v>6</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I247" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J247" t="s">
         <v>13</v>
@@ -7959,7 +7963,7 @@
     </row>
     <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B248" s="2"/>
       <c r="C248" s="2" t="s">
@@ -7974,10 +7978,10 @@
         <v>6</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I248" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J248" t="s">
         <v>13</v>
@@ -7985,7 +7989,7 @@
     </row>
     <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>1</v>
@@ -8000,10 +8004,10 @@
         <v>6</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I249" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J249" t="s">
         <v>13</v>
@@ -8011,7 +8015,7 @@
     </row>
     <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B250" s="2"/>
       <c r="C250" s="2" t="s">
@@ -8020,14 +8024,14 @@
       <c r="D250" s="2"/>
       <c r="E250" s="5"/>
       <c r="F250" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G250" s="2"/>
       <c r="H250" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I250" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J250" t="s">
         <v>13</v>
@@ -8035,7 +8039,7 @@
     </row>
     <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B251" s="2"/>
       <c r="C251" s="2" t="s">
@@ -8044,14 +8048,14 @@
       <c r="D251" s="2"/>
       <c r="E251" s="5"/>
       <c r="F251" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G251" s="2"/>
       <c r="H251" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I251" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J251" t="s">
         <v>13</v>
@@ -8059,7 +8063,7 @@
     </row>
     <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B252" s="2"/>
       <c r="C252" s="2" t="s">
@@ -8068,14 +8072,14 @@
       <c r="D252" s="2"/>
       <c r="E252" s="5"/>
       <c r="F252" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G252" s="2"/>
       <c r="H252" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I252" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J252" t="s">
         <v>13</v>
@@ -8083,7 +8087,7 @@
     </row>
     <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>1</v>
@@ -8098,10 +8102,10 @@
         <v>6</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I253" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J253" t="s">
         <v>13</v>
@@ -8109,7 +8113,7 @@
     </row>
     <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>1</v>
@@ -8118,11 +8122,11 @@
       <c r="D254" s="2"/>
       <c r="E254" s="5"/>
       <c r="F254" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G254" s="2"/>
       <c r="H254" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I254" t="s">
         <v>1</v>
@@ -8133,7 +8137,7 @@
     </row>
     <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>1</v>
@@ -8144,18 +8148,18 @@
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I255" t="s">
+        <v>1</v>
+      </c>
+      <c r="J255" t="s">
         <v>25</v>
-      </c>
-      <c r="I255" t="s">
-        <v>1</v>
-      </c>
-      <c r="J255" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>1</v>
@@ -8166,18 +8170,18 @@
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I256" t="s">
+        <v>1</v>
+      </c>
+      <c r="J256" t="s">
         <v>25</v>
-      </c>
-      <c r="I256" t="s">
-        <v>1</v>
-      </c>
-      <c r="J256" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="257" spans="1:10">
       <c r="A257" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B257" s="2"/>
       <c r="C257" s="2" t="s">
@@ -8192,10 +8196,10 @@
         <v>6</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I257" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J257" t="s">
         <v>13</v>
@@ -8203,7 +8207,7 @@
     </row>
     <row r="258" spans="1:10">
       <c r="A258" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B258" s="2"/>
       <c r="C258" s="2" t="s">
@@ -8212,14 +8216,14 @@
       <c r="D258" s="2"/>
       <c r="E258" s="5"/>
       <c r="F258" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G258" s="2"/>
       <c r="H258" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I258" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J258" t="s">
         <v>13</v>
@@ -8227,7 +8231,7 @@
     </row>
     <row r="259" spans="1:10">
       <c r="A259" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B259" s="2"/>
       <c r="C259" s="2" t="s">
@@ -8236,14 +8240,14 @@
       <c r="D259" s="2"/>
       <c r="E259" s="5"/>
       <c r="F259" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G259" s="2"/>
       <c r="H259" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I259" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J259" t="s">
         <v>13</v>
@@ -8251,7 +8255,7 @@
     </row>
     <row r="260" spans="1:10">
       <c r="A260" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B260" s="2"/>
       <c r="C260" s="2" t="s">
@@ -8260,14 +8264,14 @@
       <c r="D260" s="2"/>
       <c r="E260" s="5"/>
       <c r="F260" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G260" s="2"/>
       <c r="H260" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I260" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J260" t="s">
         <v>13</v>
@@ -8275,7 +8279,7 @@
     </row>
     <row r="261" spans="1:10">
       <c r="A261" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B261" s="2"/>
       <c r="C261" s="2" t="s">
@@ -8284,14 +8288,14 @@
       <c r="D261" s="2"/>
       <c r="E261" s="5"/>
       <c r="F261" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G261" s="2"/>
       <c r="H261" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I261" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J261" t="s">
         <v>13</v>
@@ -8299,7 +8303,7 @@
     </row>
     <row r="262" spans="1:10">
       <c r="A262" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B262" s="2"/>
       <c r="C262" s="2" t="s">
@@ -8308,14 +8312,14 @@
       <c r="D262" s="2"/>
       <c r="E262" s="5"/>
       <c r="F262" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G262" s="2"/>
       <c r="H262" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I262" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J262" t="s">
         <v>13</v>
@@ -8323,7 +8327,7 @@
     </row>
     <row r="263" spans="1:10">
       <c r="A263" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B263" s="2"/>
       <c r="C263" s="2" t="s">
@@ -8338,10 +8342,10 @@
         <v>6</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I263" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J263" t="s">
         <v>13</v>
@@ -8349,7 +8353,7 @@
     </row>
     <row r="264" spans="1:10">
       <c r="A264" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B264" s="2"/>
       <c r="C264" s="2" t="s">
@@ -8360,18 +8364,18 @@
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I264" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J264" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="265" spans="1:10">
       <c r="A265" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B265" s="2"/>
       <c r="C265" s="2" t="s">
@@ -8382,10 +8386,10 @@
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I265" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J265" t="s">
         <v>13</v>
@@ -8393,7 +8397,7 @@
     </row>
     <row r="266" spans="1:10">
       <c r="A266" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B266" s="2"/>
       <c r="C266" s="2" t="s">
@@ -8410,10 +8414,10 @@
         <v>6</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I266" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J266" t="s">
         <v>13</v>
@@ -8421,7 +8425,7 @@
     </row>
     <row r="267" spans="1:10">
       <c r="A267" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B267" s="2"/>
       <c r="C267" s="2" t="s">
@@ -8430,14 +8434,14 @@
       <c r="D267" s="2"/>
       <c r="E267" s="5"/>
       <c r="F267" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G267" s="2"/>
       <c r="H267" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I267" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J267" t="s">
         <v>13</v>
@@ -8445,7 +8449,7 @@
     </row>
     <row r="268" spans="1:10">
       <c r="A268" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>1</v>
@@ -8456,18 +8460,18 @@
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I268" t="s">
+        <v>1</v>
+      </c>
+      <c r="J268" t="s">
         <v>25</v>
-      </c>
-      <c r="I268" t="s">
-        <v>1</v>
-      </c>
-      <c r="J268" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="269" spans="1:10">
       <c r="A269" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B269" s="2"/>
       <c r="C269" s="2" t="s">
@@ -8476,14 +8480,14 @@
       <c r="D269" s="2"/>
       <c r="E269" s="5"/>
       <c r="F269" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G269" s="2"/>
       <c r="H269" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I269" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J269" t="s">
         <v>13</v>
@@ -8491,7 +8495,7 @@
     </row>
     <row r="270" spans="1:10">
       <c r="A270" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B270" s="2"/>
       <c r="C270" s="2" t="s">
@@ -8500,14 +8504,14 @@
       <c r="D270" s="2"/>
       <c r="E270" s="5"/>
       <c r="F270" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G270" s="2"/>
       <c r="H270" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I270" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J270" t="s">
         <v>13</v>
@@ -8515,7 +8519,7 @@
     </row>
     <row r="271" spans="1:10">
       <c r="A271" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B271" s="2"/>
       <c r="C271" s="2" t="s">
@@ -8524,14 +8528,14 @@
       <c r="D271" s="2"/>
       <c r="E271" s="5"/>
       <c r="F271" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G271" s="2"/>
       <c r="H271" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I271" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J271" t="s">
         <v>13</v>
@@ -8539,7 +8543,7 @@
     </row>
     <row r="272" spans="1:10">
       <c r="A272" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B272" s="2"/>
       <c r="C272" s="2" t="s">
@@ -8548,14 +8552,14 @@
       <c r="D272" s="2"/>
       <c r="E272" s="5"/>
       <c r="F272" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G272" s="2"/>
       <c r="H272" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I272" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J272" t="s">
         <v>13</v>
@@ -8563,7 +8567,7 @@
     </row>
     <row r="273" spans="1:10">
       <c r="A273" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B273" s="2"/>
       <c r="C273" s="2" t="s">
@@ -8572,14 +8576,14 @@
       <c r="D273" s="2"/>
       <c r="E273" s="5"/>
       <c r="F273" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G273" s="2"/>
       <c r="H273" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I273" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J273" t="s">
         <v>13</v>
@@ -8587,7 +8591,7 @@
     </row>
     <row r="274" spans="1:10">
       <c r="A274" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -8596,14 +8600,14 @@
         <v>4</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G274" s="2"/>
       <c r="H274" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I274" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J274" t="s">
         <v>13</v>
@@ -8611,7 +8615,7 @@
     </row>
     <row r="275" spans="1:10">
       <c r="A275" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -8620,14 +8624,14 @@
         <v>4</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G275" s="2"/>
       <c r="H275" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I275" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J275" t="s">
         <v>13</v>
@@ -8635,7 +8639,7 @@
     </row>
     <row r="276" spans="1:10">
       <c r="A276" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B276" s="2"/>
       <c r="C276" s="2" t="s">
@@ -8646,16 +8650,16 @@
         <v>4</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G276" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I276" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J276" t="s">
         <v>13</v>
@@ -8663,7 +8667,7 @@
     </row>
     <row r="277" spans="1:10">
       <c r="A277" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B277" s="2"/>
       <c r="C277" s="2" t="s">
@@ -8674,16 +8678,16 @@
         <v>4</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G277" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I277" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J277" t="s">
         <v>13</v>
@@ -8691,7 +8695,7 @@
     </row>
     <row r="278" spans="1:10">
       <c r="A278" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B278" s="2"/>
       <c r="C278" s="2" t="s">
@@ -8702,16 +8706,16 @@
         <v>4</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G278" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I278" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J278" t="s">
         <v>13</v>
@@ -8719,7 +8723,7 @@
     </row>
     <row r="279" spans="1:10">
       <c r="A279" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B279" s="2"/>
       <c r="C279" s="2" t="s">
@@ -8728,14 +8732,14 @@
       <c r="D279" s="2"/>
       <c r="E279" s="5"/>
       <c r="F279" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G279" s="2"/>
       <c r="H279" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I279" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J279" t="s">
         <v>13</v>
@@ -8743,7 +8747,7 @@
     </row>
     <row r="280" spans="1:10">
       <c r="A280" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B280" s="2"/>
       <c r="C280" s="2" t="s">
@@ -8754,10 +8758,10 @@
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I280" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J280" t="s">
         <v>13</v>
@@ -8765,7 +8769,7 @@
     </row>
     <row r="281" spans="1:10">
       <c r="A281" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>1</v>
@@ -8782,10 +8786,10 @@
         <v>6</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I281" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J281" t="s">
         <v>13</v>
@@ -8793,7 +8797,7 @@
     </row>
     <row r="282" spans="1:10">
       <c r="A282" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>1</v>
@@ -8802,11 +8806,11 @@
       <c r="D282" s="2"/>
       <c r="E282" s="5"/>
       <c r="F282" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G282" s="2"/>
       <c r="H282" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I282" t="s">
         <v>1</v>
@@ -8817,7 +8821,7 @@
     </row>
     <row r="283" spans="1:10">
       <c r="A283" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B283" s="2"/>
       <c r="C283" s="2" t="s">
@@ -8828,18 +8832,18 @@
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I283" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J283" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="284" spans="1:10">
       <c r="A284" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B284" s="2"/>
       <c r="C284" s="2" t="s">
@@ -8848,14 +8852,14 @@
       <c r="D284" s="2"/>
       <c r="E284" s="5"/>
       <c r="F284" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G284" s="2"/>
       <c r="H284" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I284" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J284" t="s">
         <v>13</v>
@@ -8863,7 +8867,7 @@
     </row>
     <row r="285" spans="1:10">
       <c r="A285" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B285" s="2"/>
       <c r="C285" s="2" t="s">
@@ -8872,14 +8876,14 @@
       <c r="D285" s="2"/>
       <c r="E285" s="5"/>
       <c r="F285" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G285" s="2"/>
       <c r="H285" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I285" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J285" t="s">
         <v>13</v>
@@ -8887,7 +8891,7 @@
     </row>
     <row r="286" spans="1:10">
       <c r="A286" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B286" s="2"/>
       <c r="C286" s="2" t="s">
@@ -8896,14 +8900,14 @@
       <c r="D286" s="2"/>
       <c r="E286" s="5"/>
       <c r="F286" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G286" s="2"/>
       <c r="H286" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I286" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J286" t="s">
         <v>13</v>
@@ -8911,7 +8915,7 @@
     </row>
     <row r="287" spans="1:10">
       <c r="A287" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B287" s="2"/>
       <c r="C287" s="2" t="s">
@@ -8922,10 +8926,10 @@
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I287" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J287" t="s">
         <v>13</v>
@@ -8933,7 +8937,7 @@
     </row>
     <row r="288" spans="1:10">
       <c r="A288" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B288" s="2"/>
       <c r="C288" s="2" t="s">
@@ -8947,7 +8951,7 @@
         <v>11</v>
       </c>
       <c r="I288" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J288" t="s">
         <v>13</v>
@@ -8955,7 +8959,7 @@
     </row>
     <row r="289" spans="1:10">
       <c r="A289" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B289" s="2"/>
       <c r="C289" s="2" t="s">
@@ -8970,10 +8974,10 @@
         <v>6</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I289" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J289" t="s">
         <v>13</v>
@@ -8981,7 +8985,7 @@
     </row>
     <row r="290" spans="1:10">
       <c r="A290" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>1</v>
@@ -8992,16 +8996,16 @@
       <c r="D290" s="2"/>
       <c r="E290" s="5"/>
       <c r="F290" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G290" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I290" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J290" t="s">
         <v>13</v>
@@ -9009,7 +9013,7 @@
     </row>
     <row r="291" spans="1:10">
       <c r="A291" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B291" s="2"/>
       <c r="C291" s="2" t="s">
@@ -9024,10 +9028,10 @@
         <v>6</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I291" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J291" t="s">
         <v>13</v>
@@ -9035,7 +9039,7 @@
     </row>
     <row r="292" spans="1:10">
       <c r="A292" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>1</v>
@@ -9050,10 +9054,10 @@
         <v>6</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I292" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J292" t="s">
         <v>13</v>
@@ -9061,7 +9065,7 @@
     </row>
     <row r="293" spans="1:10">
       <c r="A293" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>1</v>
@@ -9072,7 +9076,7 @@
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I293" t="s">
         <v>1</v>
@@ -9083,7 +9087,7 @@
     </row>
     <row r="294" spans="1:10">
       <c r="A294" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B294" s="2"/>
       <c r="C294" s="2" t="s">
@@ -9094,10 +9098,10 @@
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I294" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J294" t="s">
         <v>13</v>
@@ -9105,7 +9109,7 @@
     </row>
     <row r="295" spans="1:10">
       <c r="A295" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>1</v>
@@ -9122,10 +9126,10 @@
         <v>6</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I295" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J295" t="s">
         <v>13</v>
@@ -9133,7 +9137,7 @@
     </row>
     <row r="296" spans="1:10">
       <c r="A296" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>1</v>
@@ -9144,18 +9148,18 @@
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I296" t="s">
+        <v>1</v>
+      </c>
+      <c r="J296" t="s">
         <v>25</v>
-      </c>
-      <c r="I296" t="s">
-        <v>1</v>
-      </c>
-      <c r="J296" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="297" spans="1:10">
       <c r="A297" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B297" s="2"/>
       <c r="C297" s="2" t="s">
@@ -9170,10 +9174,10 @@
         <v>6</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I297" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J297" t="s">
         <v>13</v>
@@ -9181,7 +9185,7 @@
     </row>
     <row r="298" spans="1:10">
       <c r="A298" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B298" s="2"/>
       <c r="C298" s="2" t="s">
@@ -9192,10 +9196,10 @@
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I298" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J298" t="s">
         <v>13</v>
@@ -9203,7 +9207,7 @@
     </row>
     <row r="299" spans="1:10">
       <c r="A299" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B299" s="2"/>
       <c r="C299" s="2" t="s">
@@ -9214,10 +9218,10 @@
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I299" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J299" t="s">
         <v>13</v>
@@ -9225,7 +9229,7 @@
     </row>
     <row r="300" spans="1:10">
       <c r="A300" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B300" s="2"/>
       <c r="C300" s="2" t="s">
@@ -9234,14 +9238,14 @@
       <c r="D300" s="2"/>
       <c r="E300" s="5"/>
       <c r="F300" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G300" s="2"/>
       <c r="H300" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I300" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J300" t="s">
         <v>13</v>
@@ -9249,7 +9253,7 @@
     </row>
     <row r="301" spans="1:10">
       <c r="A301" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>1</v>
@@ -9260,18 +9264,18 @@
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I301" t="s">
+        <v>1</v>
+      </c>
+      <c r="J301" t="s">
         <v>25</v>
-      </c>
-      <c r="I301" t="s">
-        <v>1</v>
-      </c>
-      <c r="J301" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="302" spans="1:10">
       <c r="A302" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>1</v>
@@ -9282,18 +9286,18 @@
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I302" t="s">
+        <v>1</v>
+      </c>
+      <c r="J302" t="s">
         <v>25</v>
-      </c>
-      <c r="I302" t="s">
-        <v>1</v>
-      </c>
-      <c r="J302" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="303" spans="1:10">
       <c r="A303" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>1</v>
@@ -9302,11 +9306,11 @@
       <c r="D303" s="2"/>
       <c r="E303" s="5"/>
       <c r="F303" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G303" s="2"/>
       <c r="H303" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I303" t="s">
         <v>1</v>
@@ -9317,7 +9321,7 @@
     </row>
     <row r="304" spans="1:10">
       <c r="A304" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B304" s="2"/>
       <c r="C304" s="2" t="s">
@@ -9326,14 +9330,14 @@
       <c r="D304" s="2"/>
       <c r="E304" s="5"/>
       <c r="F304" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G304" s="2"/>
       <c r="H304" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I304" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J304" t="s">
         <v>13</v>
@@ -9341,7 +9345,7 @@
     </row>
     <row r="305" spans="1:10">
       <c r="A305" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B305" s="2"/>
       <c r="C305" s="2" t="s">
@@ -9350,14 +9354,14 @@
       <c r="D305" s="2"/>
       <c r="E305" s="5"/>
       <c r="F305" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G305" s="2"/>
       <c r="H305" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I305" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J305" t="s">
         <v>13</v>
@@ -9365,7 +9369,7 @@
     </row>
     <row r="306" spans="1:10">
       <c r="A306" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B306" s="2"/>
       <c r="C306" s="2" t="s">
@@ -9374,14 +9378,14 @@
       <c r="D306" s="2"/>
       <c r="E306" s="5"/>
       <c r="F306" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G306" s="2"/>
       <c r="H306" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I306" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J306" t="s">
         <v>13</v>
@@ -9389,7 +9393,7 @@
     </row>
     <row r="307" spans="1:10">
       <c r="A307" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B307" s="2"/>
       <c r="C307" s="2" t="s">
@@ -9404,10 +9408,10 @@
         <v>6</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I307" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J307" t="s">
         <v>13</v>
@@ -9415,7 +9419,7 @@
     </row>
     <row r="308" spans="1:10">
       <c r="A308" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>1</v>
@@ -9426,7 +9430,7 @@
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I308" t="s">
         <v>1</v>
@@ -9437,7 +9441,7 @@
     </row>
     <row r="309" spans="1:10">
       <c r="A309" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>1</v>
@@ -9448,7 +9452,7 @@
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I309" t="s">
         <v>1</v>
@@ -9459,7 +9463,7 @@
     </row>
     <row r="310" spans="1:10">
       <c r="A310" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>1</v>
@@ -9470,7 +9474,7 @@
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I310" t="s">
         <v>1</v>
@@ -9481,7 +9485,7 @@
     </row>
     <row r="311" spans="1:10">
       <c r="A311" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B311" s="2"/>
       <c r="C311" s="2" t="s">
@@ -9490,14 +9494,14 @@
       <c r="D311" s="2"/>
       <c r="E311" s="5"/>
       <c r="F311" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G311" s="2"/>
       <c r="H311" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I311" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J311" t="s">
         <v>13</v>
@@ -9505,7 +9509,7 @@
     </row>
     <row r="312" spans="1:10">
       <c r="A312" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B312" s="2"/>
       <c r="C312" s="2" t="s">
@@ -9516,10 +9520,10 @@
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I312" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J312" t="s">
         <v>13</v>
@@ -9527,7 +9531,7 @@
     </row>
     <row r="313" spans="1:10">
       <c r="A313" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -9538,10 +9542,10 @@
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I313" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J313" t="s">
         <v>13</v>
@@ -9549,7 +9553,7 @@
     </row>
     <row r="314" spans="1:10">
       <c r="A314" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>1</v>
@@ -9564,10 +9568,10 @@
         <v>6</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I314" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J314" t="s">
         <v>13</v>
@@ -9575,7 +9579,7 @@
     </row>
     <row r="315" spans="1:10">
       <c r="A315" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B315" s="2"/>
       <c r="C315" s="2" t="s">
@@ -9586,10 +9590,10 @@
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I315" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J315" t="s">
         <v>13</v>
@@ -9597,7 +9601,7 @@
     </row>
     <row r="316" spans="1:10">
       <c r="A316" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B316" s="2"/>
       <c r="C316" s="2" t="s">
@@ -9610,10 +9614,10 @@
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I316" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J316" t="s">
         <v>13</v>
@@ -9621,7 +9625,7 @@
     </row>
     <row r="317" spans="1:10">
       <c r="A317" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B317" s="2"/>
       <c r="C317" s="2" t="s">
@@ -9636,10 +9640,10 @@
         <v>6</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I317" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J317" t="s">
         <v>13</v>
@@ -9647,7 +9651,7 @@
     </row>
     <row r="318" spans="1:10">
       <c r="A318" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B318" s="2"/>
       <c r="C318" s="2" t="s">
@@ -9662,10 +9666,10 @@
         <v>6</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I318" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J318" t="s">
         <v>13</v>
@@ -9673,7 +9677,7 @@
     </row>
     <row r="319" spans="1:10">
       <c r="A319" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B319" s="2"/>
       <c r="C319" s="2" t="s">
@@ -9682,14 +9686,14 @@
       <c r="D319" s="2"/>
       <c r="E319" s="5"/>
       <c r="F319" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G319" s="2"/>
       <c r="H319" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I319" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J319" t="s">
         <v>13</v>
@@ -9697,7 +9701,7 @@
     </row>
     <row r="320" spans="1:10">
       <c r="A320" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>1</v>
@@ -9712,10 +9716,10 @@
         <v>6</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I320" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J320" t="s">
         <v>13</v>
@@ -9723,7 +9727,7 @@
     </row>
     <row r="321" spans="1:10">
       <c r="A321" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B321" s="2"/>
       <c r="C321" s="2" t="s">
@@ -9738,10 +9742,10 @@
         <v>6</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I321" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J321" t="s">
         <v>13</v>
@@ -9749,7 +9753,7 @@
     </row>
     <row r="322" spans="1:10">
       <c r="A322" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B322" s="2"/>
       <c r="C322" s="2" t="s">
@@ -9758,14 +9762,14 @@
       <c r="D322" s="2"/>
       <c r="E322" s="5"/>
       <c r="F322" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G322" s="2"/>
       <c r="H322" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I322" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J322" t="s">
         <v>13</v>
@@ -9773,7 +9777,7 @@
     </row>
     <row r="323" spans="1:10">
       <c r="A323" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B323" s="2"/>
       <c r="C323" s="2" t="s">
@@ -9782,14 +9786,14 @@
       <c r="D323" s="2"/>
       <c r="E323" s="5"/>
       <c r="F323" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G323" s="2"/>
       <c r="H323" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I323" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J323" t="s">
         <v>13</v>
@@ -9797,7 +9801,7 @@
     </row>
     <row r="324" spans="1:10">
       <c r="A324" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B324" s="2"/>
       <c r="C324" s="2" t="s">
@@ -9812,10 +9816,10 @@
         <v>6</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I324" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J324" t="s">
         <v>13</v>
@@ -9823,7 +9827,7 @@
     </row>
     <row r="325" spans="1:10">
       <c r="A325" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -9834,10 +9838,10 @@
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I325" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J325" t="s">
         <v>13</v>
@@ -9845,7 +9849,7 @@
     </row>
     <row r="326" spans="1:10">
       <c r="A326" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>1</v>
@@ -9854,11 +9858,11 @@
       <c r="D326" s="2"/>
       <c r="E326" s="5"/>
       <c r="F326" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G326" s="2"/>
       <c r="H326" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I326" t="s">
         <v>1</v>
@@ -9869,7 +9873,7 @@
     </row>
     <row r="327" spans="1:10">
       <c r="A327" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B327" s="2"/>
       <c r="C327" s="2" t="s">
@@ -9878,14 +9882,14 @@
       <c r="D327" s="2"/>
       <c r="E327" s="5"/>
       <c r="F327" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G327" s="2"/>
       <c r="H327" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I327" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J327" t="s">
         <v>13</v>
@@ -9893,7 +9897,7 @@
     </row>
     <row r="328" spans="1:10">
       <c r="A328" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>1</v>
@@ -9910,10 +9914,10 @@
         <v>6</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I328" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J328" t="s">
         <v>13</v>
@@ -9921,7 +9925,7 @@
     </row>
     <row r="329" spans="1:10">
       <c r="A329" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>1</v>
@@ -9936,10 +9940,10 @@
         <v>6</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I329" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J329" t="s">
         <v>13</v>
@@ -9947,7 +9951,7 @@
     </row>
     <row r="330" spans="1:10">
       <c r="A330" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B330" s="2"/>
       <c r="C330" s="2" t="s">
@@ -9956,14 +9960,14 @@
       <c r="D330" s="2"/>
       <c r="E330" s="5"/>
       <c r="F330" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G330" s="2"/>
       <c r="H330" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I330" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J330" t="s">
         <v>13</v>
@@ -9971,7 +9975,7 @@
     </row>
     <row r="331" spans="1:10">
       <c r="A331" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -9982,10 +9986,10 @@
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I331" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J331" t="s">
         <v>13</v>
@@ -9993,7 +9997,7 @@
     </row>
     <row r="332" spans="1:10">
       <c r="A332" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B332" s="2"/>
       <c r="C332" s="2" t="s">
@@ -10008,10 +10012,10 @@
         <v>6</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I332" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J332" t="s">
         <v>13</v>
@@ -10019,7 +10023,7 @@
     </row>
     <row r="333" spans="1:10">
       <c r="A333" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B333" s="2"/>
       <c r="C333" s="2" t="s">
@@ -10030,10 +10034,10 @@
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I333" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J333" t="s">
         <v>13</v>
@@ -10041,7 +10045,7 @@
     </row>
     <row r="334" spans="1:10">
       <c r="A334" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B334" s="2"/>
       <c r="C334" s="2" t="s">
@@ -10052,10 +10056,10 @@
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I334" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J334" t="s">
         <v>13</v>
@@ -10063,7 +10067,7 @@
     </row>
     <row r="335" spans="1:10">
       <c r="A335" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B335" s="2"/>
       <c r="C335" s="2" t="s">
@@ -10074,10 +10078,10 @@
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I335" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J335" t="s">
         <v>13</v>
@@ -10085,7 +10089,7 @@
     </row>
     <row r="336" spans="1:10">
       <c r="A336" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B336" s="2"/>
       <c r="C336" s="2" t="s">
@@ -10098,7 +10102,7 @@
       </c>
       <c r="G336" s="2"/>
       <c r="H336" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I336" t="s">
         <v>12</v>
@@ -10109,7 +10113,7 @@
     </row>
     <row r="337" spans="1:10">
       <c r="A337" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B337" s="2"/>
       <c r="C337" s="2" t="s">
@@ -10118,14 +10122,14 @@
       <c r="D337" s="2"/>
       <c r="E337" s="5"/>
       <c r="F337" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G337" s="2"/>
       <c r="H337" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I337" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J337" t="s">
         <v>13</v>
@@ -10133,7 +10137,7 @@
     </row>
     <row r="338" spans="1:10">
       <c r="A338" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B338" s="2"/>
       <c r="C338" s="2" t="s">
@@ -10144,10 +10148,10 @@
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I338" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J338" t="s">
         <v>13</v>
@@ -10155,7 +10159,7 @@
     </row>
     <row r="339" spans="1:10">
       <c r="A339" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>1</v>
@@ -10164,22 +10168,22 @@
       <c r="D339" s="2"/>
       <c r="E339" s="5"/>
       <c r="F339" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G339" s="2"/>
       <c r="H339" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I339" t="s">
         <v>1</v>
       </c>
       <c r="J339" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="340" spans="1:10">
       <c r="A340" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>1</v>
@@ -10194,10 +10198,10 @@
         <v>6</v>
       </c>
       <c r="H340" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I340" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J340" t="s">
         <v>13</v>
@@ -10205,7 +10209,7 @@
     </row>
     <row r="341" spans="1:10">
       <c r="A341" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B341" s="2"/>
       <c r="C341" s="2" t="s">
@@ -10214,14 +10218,14 @@
       <c r="D341" s="2"/>
       <c r="E341" s="5"/>
       <c r="F341" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G341" s="2"/>
       <c r="H341" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I341" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J341" t="s">
         <v>13</v>
@@ -10229,7 +10233,7 @@
     </row>
     <row r="342" spans="1:10">
       <c r="A342" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>1</v>
@@ -10238,11 +10242,11 @@
       <c r="D342" s="2"/>
       <c r="E342" s="5"/>
       <c r="F342" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G342" s="2"/>
       <c r="H342" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I342" t="s">
         <v>1</v>
@@ -10253,7 +10257,7 @@
     </row>
     <row r="343" spans="1:10">
       <c r="A343" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>1</v>
@@ -10262,11 +10266,11 @@
       <c r="D343" s="2"/>
       <c r="E343" s="5"/>
       <c r="F343" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G343" s="2"/>
       <c r="H343" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I343" t="s">
         <v>1</v>
@@ -10277,7 +10281,7 @@
     </row>
     <row r="344" spans="1:10">
       <c r="A344" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B344" s="2"/>
       <c r="C344" s="2" t="s">
@@ -10286,14 +10290,14 @@
       <c r="D344" s="2"/>
       <c r="E344" s="5"/>
       <c r="F344" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G344" s="2"/>
       <c r="H344" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I344" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J344" t="s">
         <v>13</v>
@@ -10301,7 +10305,7 @@
     </row>
     <row r="345" spans="1:10">
       <c r="A345" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>1</v>
@@ -10310,11 +10314,11 @@
       <c r="D345" s="2"/>
       <c r="E345" s="5"/>
       <c r="F345" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G345" s="2"/>
       <c r="H345" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I345" t="s">
         <v>1</v>
@@ -10325,7 +10329,7 @@
     </row>
     <row r="346" spans="1:10">
       <c r="A346" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B346" s="2"/>
       <c r="C346" s="2" t="s">
@@ -10336,10 +10340,10 @@
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I346" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J346" t="s">
         <v>13</v>
@@ -10347,7 +10351,7 @@
     </row>
     <row r="347" spans="1:10">
       <c r="A347" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>1</v>
@@ -10362,10 +10366,10 @@
         <v>6</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I347" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J347" t="s">
         <v>13</v>
@@ -10373,7 +10377,7 @@
     </row>
     <row r="348" spans="1:10">
       <c r="A348" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B348" s="2"/>
       <c r="C348" s="2" t="s">
@@ -10384,18 +10388,18 @@
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I348" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J348" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="349" spans="1:10">
       <c r="A349" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>1</v>
@@ -10410,10 +10414,10 @@
         <v>6</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I349" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J349" t="s">
         <v>13</v>
@@ -10421,7 +10425,7 @@
     </row>
     <row r="350" spans="1:10">
       <c r="A350" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B350" s="2"/>
       <c r="C350" s="2" t="s">
@@ -10436,10 +10440,10 @@
         <v>6</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I350" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J350" t="s">
         <v>13</v>
@@ -10447,7 +10451,7 @@
     </row>
     <row r="351" spans="1:10">
       <c r="A351" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B351" s="2"/>
       <c r="C351" s="2" t="s">
@@ -10462,10 +10466,10 @@
         <v>6</v>
       </c>
       <c r="H351" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I351" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J351" t="s">
         <v>13</v>
@@ -10473,7 +10477,7 @@
     </row>
     <row r="352" spans="1:10">
       <c r="A352" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B352" s="2"/>
       <c r="C352" s="2" t="s">
@@ -10488,10 +10492,10 @@
         <v>6</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I352" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J352" t="s">
         <v>13</v>
@@ -10499,7 +10503,7 @@
     </row>
     <row r="353" spans="1:10">
       <c r="A353" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B353" s="2"/>
       <c r="C353" s="2" t="s">
@@ -10508,14 +10512,14 @@
       <c r="D353" s="2"/>
       <c r="E353" s="5"/>
       <c r="F353" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G353" s="2"/>
       <c r="H353" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I353" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J353" t="s">
         <v>13</v>
@@ -10530,7 +10534,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782676695" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782868662" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10539,14 +10543,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782676695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782676695" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782868662" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782868662" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782676695" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782868662" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/MovieCatalog.xlsx
+++ b/MovieCatalog.xlsx
@@ -16,10 +16,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1782868662" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1782868662" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1782868662" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1782868662"/>
+      <pm:revision xmlns:pm="smNativeData" day="1782869296" val="1224" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1782869296" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1782869296" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1782869296"/>
     </ext>
   </extLst>
 </workbook>
@@ -228,10 +228,10 @@
     <t>Back to the Future III</t>
   </si>
   <si>
-    <t>Bahubali - The Beginning</t>
-  </si>
-  <si>
-    <t>Bahubali - The Conslusion</t>
+    <t>Bahubali: The Beginning</t>
+  </si>
+  <si>
+    <t>Bahubali 2: The Conslusion</t>
   </si>
   <si>
     <t>Bajirao Mastani</t>
@@ -971,7 +971,7 @@
     <t>Matrix Revolutions</t>
   </si>
   <si>
-    <t>Mee Shivajiraje Bhsale Boltoy</t>
+    <t>Mee Shivajiraje Bhosale Boltoy</t>
   </si>
   <si>
     <t>Men of Honor</t>
@@ -1450,7 +1450,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1465,7 +1465,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -1481,7 +1481,7 @@
       <vertAlign val="superscript"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1" ssSize="66" ssDistance="15">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1497,7 +1497,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782868662" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1782869296" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1519,7 +1519,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1533,7 +1533,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="76" fgClr="00FFFF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1547,7 +1547,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1558,7 +1558,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782868662" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1782869296" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1580,7 +1580,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
+          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
         </ext>
       </extLst>
     </border>
@@ -1599,7 +1599,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662">
+          <pm:border xmlns:pm="smNativeData" id="1782869296">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1623,7 +1623,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662">
+          <pm:border xmlns:pm="smNativeData" id="1782869296">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1647,7 +1647,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662">
+          <pm:border xmlns:pm="smNativeData" id="1782869296">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1670,7 +1670,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662">
+          <pm:border xmlns:pm="smNativeData" id="1782869296">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1693,7 +1693,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
+          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
         </ext>
       </extLst>
     </border>
@@ -1712,7 +1712,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782868662"/>
+          <pm:border xmlns:pm="smNativeData" id="1782869296"/>
         </ext>
       </extLst>
     </border>
@@ -1735,10 +1735,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1782868662" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1782869296" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1782868662" count="2">
+      <pm:colors xmlns:pm="smNativeData" id="1782869296" count="2">
         <pm:color name="Color 24" rgb="FFFF3D"/>
         <pm:color name="Color 25" rgb="FFFF9E"/>
       </pm:colors>
@@ -7214,7 +7214,7 @@
         <v>1</v>
       </c>
       <c r="J216" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217" spans="1:10">
@@ -7418,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="J224" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
     </row>
     <row r="225" spans="1:10">
@@ -10534,7 +10534,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782868662" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1782869296" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10543,14 +10543,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782868662" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782868662" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1782869296" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1782869296" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782868662" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782869296" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
